--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_antofagasta.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2023_antofagasta.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -723,10 +723,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1019165.12</v>
+        <v>1019165.13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>997639</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -778,7 +778,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>998159.12</v>
+        <v>998159.13</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>803301.44</v>
@@ -836,7 +836,7 @@
         <v>1057160.25</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1054778.62</v>
+        <v>1054778.63</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>844828.88</v>
@@ -866,7 +866,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1046384.62</v>
+        <v>1046384.63</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>845150.88</v>
@@ -910,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1049986.62</v>
+        <v>1049986.63</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -921,7 +921,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1110992.62</v>
+        <v>1110992.63</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>898176.25</v>
@@ -932,7 +932,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1059210.12</v>
+        <v>1059210.13</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>857913</v>
@@ -987,7 +987,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1101627.12</v>
+        <v>1101627.13</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>891079.38</v>
@@ -1001,7 +1001,7 @@
         <v>1094392.75</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>1078830.75</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1064,7 +1064,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1102613.12</v>
+        <v>1102613.13</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>886398.88</v>
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1134754.62</v>
+        <v>1134754.63</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>900212.25</v>
@@ -1166,7 +1166,7 @@
         <v>1156185.5</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1262,7 +1262,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>1219264.62</v>
+        <v>1219264.63</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>1023105.81</v>
@@ -1273,7 +1273,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>1232960.12</v>
+        <v>1232960.13</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>1035374.06</v>
@@ -1287,7 +1287,7 @@
         <v>1233429.88</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1295,10 +1295,10 @@
         <v>57</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1274164.12</v>
+        <v>1274164.13</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>1306410.62</v>
+        <v>1306410.63</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1086115.25</v>
@@ -1342,7 +1342,7 @@
         <v>1349504.88</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1361,10 +1361,10 @@
         <v>63</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1397281.62</v>
+        <v>1397281.63</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1383,7 +1383,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1366227.12</v>
+        <v>1366227.13</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>1158414.88</v>
@@ -1416,10 +1416,10 @@
         <v>68</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1382311.62</v>
+        <v>1382311.63</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1427,7 +1427,7 @@
         <v>69</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1408310.12</v>
+        <v>1408310.13</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>1185328.75</v>
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1491702.12</v>
+        <v>1491702.13</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>1246393.5</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1447054.12</v>
+        <v>1447054.13</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1214165.25</v>
@@ -1518,7 +1518,7 @@
         <v>1457652.88</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1551,7 +1551,7 @@
         <v>1466025.38</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1559,10 +1559,10 @@
         <v>81</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>1512387.62</v>
+        <v>1512387.63</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1570,7 +1570,7 @@
         <v>82</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1503245.62</v>
+        <v>1503245.63</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>1271870.5</v>
@@ -1584,7 +1584,7 @@
         <v>1574851.75</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
